--- a/اسماء شركات الاسنان جاهزة للاستيراد/Waad_List_Import.xlsx
+++ b/اسماء شركات الاسنان جاهزة للاستيراد/Waad_List_Import.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B57E4-7E24-4C11-ACCB-13B19EBEACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="المستفيدين" state="visible" r:id="rId4"/>
+    <sheet name="المستفيدين" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="322">
   <si>
     <t>اسم المستفيد</t>
   </si>
@@ -941,19 +945,55 @@
   </si>
   <si>
     <t>1963-09-12</t>
+  </si>
+  <si>
+    <t>فرج محمد رمضان الكوافي</t>
+  </si>
+  <si>
+    <t>18/11/1988</t>
+  </si>
+  <si>
+    <t>WAAD20250001</t>
+  </si>
+  <si>
+    <t>جوري فرج محمد الكوافي</t>
+  </si>
+  <si>
+    <t>19/6/2020</t>
+  </si>
+  <si>
+    <t>WAAD20250001D1</t>
+  </si>
+  <si>
+    <t>جنان فرج محمد الكوافي</t>
+  </si>
+  <si>
+    <t>19/4/2022</t>
+  </si>
+  <si>
+    <t>WAAD20250001D2</t>
+  </si>
+  <si>
+    <t>جمان فرج محمد الكوافي</t>
+  </si>
+  <si>
+    <t>27/5/2024</t>
+  </si>
+  <si>
+    <t>WAAD20250001D3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1316,11 +1356,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C105"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C109"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1331,7 +1375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1342,7 +1386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1353,7 +1397,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1364,7 +1408,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1375,7 +1419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1386,7 +1430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1397,7 +1441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1408,7 +1452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1419,7 +1463,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1430,7 +1474,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1441,7 +1485,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1452,7 +1496,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1463,7 +1507,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1474,7 +1518,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1485,7 +1529,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1496,7 +1540,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1507,7 +1551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1518,7 +1562,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -1529,7 +1573,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1540,7 +1584,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -1551,7 +1595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1562,7 +1606,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -1573,7 +1617,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1584,7 +1628,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -1595,7 +1639,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -1606,7 +1650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -1617,7 +1661,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -1628,7 +1672,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -1639,7 +1683,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -1650,7 +1694,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -1661,7 +1705,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -1672,7 +1716,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -1683,7 +1727,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -1694,7 +1738,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -1705,7 +1749,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -1716,7 +1760,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -1727,7 +1771,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -1738,7 +1782,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -1749,7 +1793,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -1760,7 +1804,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -1771,7 +1815,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -1782,7 +1826,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -1793,7 +1837,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -1804,7 +1848,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -1815,7 +1859,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -1826,7 +1870,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -1837,7 +1881,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -1848,7 +1892,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>143</v>
       </c>
@@ -1859,7 +1903,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>146</v>
       </c>
@@ -1870,7 +1914,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>149</v>
       </c>
@@ -1881,7 +1925,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>152</v>
       </c>
@@ -1892,7 +1936,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>155</v>
       </c>
@@ -1903,7 +1947,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>158</v>
       </c>
@@ -1914,7 +1958,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>161</v>
       </c>
@@ -1925,7 +1969,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>164</v>
       </c>
@@ -1936,7 +1980,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -1947,7 +1991,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -1958,7 +2002,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -1969,7 +2013,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -1980,7 +2024,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -1991,7 +2035,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -2002,7 +2046,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -2013,7 +2057,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>188</v>
       </c>
@@ -2024,7 +2068,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -2035,7 +2079,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>194</v>
       </c>
@@ -2046,7 +2090,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -2057,7 +2101,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>200</v>
       </c>
@@ -2068,7 +2112,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>203</v>
       </c>
@@ -2079,7 +2123,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>206</v>
       </c>
@@ -2090,7 +2134,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>209</v>
       </c>
@@ -2101,7 +2145,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>212</v>
       </c>
@@ -2112,7 +2156,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>215</v>
       </c>
@@ -2123,7 +2167,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>218</v>
       </c>
@@ -2134,7 +2178,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>221</v>
       </c>
@@ -2145,7 +2189,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>224</v>
       </c>
@@ -2156,7 +2200,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>227</v>
       </c>
@@ -2167,7 +2211,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -2178,7 +2222,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -2189,7 +2233,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>236</v>
       </c>
@@ -2200,7 +2244,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>239</v>
       </c>
@@ -2211,7 +2255,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>242</v>
       </c>
@@ -2222,7 +2266,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>245</v>
       </c>
@@ -2233,7 +2277,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
@@ -2244,7 +2288,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>250</v>
       </c>
@@ -2255,7 +2299,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>253</v>
       </c>
@@ -2266,7 +2310,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -2277,7 +2321,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>258</v>
       </c>
@@ -2288,7 +2332,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>261</v>
       </c>
@@ -2299,7 +2343,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>264</v>
       </c>
@@ -2310,7 +2354,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>267</v>
       </c>
@@ -2321,7 +2365,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>270</v>
       </c>
@@ -2332,7 +2376,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>272</v>
       </c>
@@ -2343,7 +2387,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>275</v>
       </c>
@@ -2354,7 +2398,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>277</v>
       </c>
@@ -2365,7 +2409,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>280</v>
       </c>
@@ -2376,7 +2420,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>283</v>
       </c>
@@ -2387,7 +2431,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>286</v>
       </c>
@@ -2398,7 +2442,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>289</v>
       </c>
@@ -2409,7 +2453,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>292</v>
       </c>
@@ -2420,7 +2464,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>295</v>
       </c>
@@ -2431,7 +2475,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>298</v>
       </c>
@@ -2442,7 +2486,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>301</v>
       </c>
@@ -2453,7 +2497,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>304</v>
       </c>
@@ -2475,8 +2519,52 @@
         <v>309</v>
       </c>
     </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>310</v>
+      </c>
+      <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>313</v>
+      </c>
+      <c r="B107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>316</v>
+      </c>
+      <c r="B108" t="s">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>319</v>
+      </c>
+      <c r="B109" t="s">
+        <v>321</v>
+      </c>
+      <c r="C109" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/اسماء شركات الاسنان جاهزة للاستيراد/Waad_List_Import.xlsx
+++ b/اسماء شركات الاسنان جاهزة للاستيراد/Waad_List_Import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B57E4-7E24-4C11-ACCB-13B19EBEACB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5F303A-FDC3-4EE3-BCD7-236E9BF4A769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="325">
   <si>
     <t>اسم المستفيد</t>
   </si>
@@ -890,27 +890,18 @@
     <t>WAAD20250030FM1</t>
   </si>
   <si>
-    <t>1955-11-26</t>
-  </si>
-  <si>
     <t>ايه مصطفى الصديق</t>
   </si>
   <si>
     <t>WAAD20250031</t>
   </si>
   <si>
-    <t>2001-09-23</t>
-  </si>
-  <si>
     <t>مصطفى بشير الصديق</t>
   </si>
   <si>
     <t>WAAD20250031F1</t>
   </si>
   <si>
-    <t>1952-07-03</t>
-  </si>
-  <si>
     <t>سهير عمر اولاد بعيو</t>
   </si>
   <si>
@@ -944,9 +935,6 @@
     <t>WAAD20250032M1</t>
   </si>
   <si>
-    <t>1963-09-12</t>
-  </si>
-  <si>
     <t>فرج محمد رمضان الكوافي</t>
   </si>
   <si>
@@ -981,12 +969,36 @@
   </si>
   <si>
     <t>WAAD20250001D3</t>
+  </si>
+  <si>
+    <t>محمد بن ناصر علي</t>
+  </si>
+  <si>
+    <t>بن ناصر علي محمود</t>
+  </si>
+  <si>
+    <t>منى عمر يونس</t>
+  </si>
+  <si>
+    <t>WAAD20250033</t>
+  </si>
+  <si>
+    <t>WAAD20250033F1</t>
+  </si>
+  <si>
+    <t>WAAD20250033M1</t>
+  </si>
+  <si>
+    <t>16/05/1977</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1016,8 +1028,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1357,14 +1370,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1375,1192 +1389,1225 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>36</v>
       </c>
       <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
       <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>60</v>
       </c>
       <c r="B21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>63</v>
       </c>
       <c r="B22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
       <c r="B24" t="s">
         <v>70</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>75</v>
       </c>
       <c r="B26" t="s">
         <v>76</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
       <c r="B27" t="s">
         <v>79</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>81</v>
       </c>
       <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>84</v>
       </c>
       <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>87</v>
       </c>
       <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>90</v>
       </c>
       <c r="B31" t="s">
         <v>91</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>93</v>
       </c>
       <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>99</v>
       </c>
       <c r="B34" t="s">
         <v>100</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>102</v>
       </c>
       <c r="B35" t="s">
         <v>103</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>105</v>
       </c>
       <c r="B36" t="s">
         <v>106</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>108</v>
       </c>
       <c r="B37" t="s">
         <v>109</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>111</v>
       </c>
       <c r="B38" t="s">
         <v>112</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>114</v>
       </c>
       <c r="B39" t="s">
         <v>115</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>117</v>
       </c>
       <c r="B40" t="s">
         <v>118</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>120</v>
       </c>
       <c r="B41" t="s">
         <v>121</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
       <c r="B42" t="s">
         <v>124</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>126</v>
       </c>
       <c r="B43" t="s">
         <v>127</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>129</v>
       </c>
       <c r="B44" t="s">
         <v>130</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45" t="s">
         <v>133</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
       <c r="B46" t="s">
         <v>135</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
       <c r="B47" t="s">
         <v>138</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
       <c r="B48" t="s">
         <v>141</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>143</v>
       </c>
       <c r="B49" t="s">
         <v>144</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>146</v>
       </c>
       <c r="B50" t="s">
         <v>147</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>149</v>
       </c>
       <c r="B51" t="s">
         <v>150</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>152</v>
       </c>
       <c r="B52" t="s">
         <v>153</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>155</v>
       </c>
       <c r="B53" t="s">
         <v>156</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>158</v>
       </c>
       <c r="B54" t="s">
         <v>159</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>161</v>
       </c>
       <c r="B55" t="s">
         <v>162</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="1" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>164</v>
       </c>
       <c r="B56" t="s">
         <v>165</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="1" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>167</v>
       </c>
       <c r="B57" t="s">
         <v>168</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>170</v>
       </c>
       <c r="B58" t="s">
         <v>171</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="1" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>173</v>
       </c>
       <c r="B59" t="s">
         <v>174</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>176</v>
       </c>
       <c r="B60" t="s">
         <v>177</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>179</v>
       </c>
       <c r="B61" t="s">
         <v>180</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>182</v>
       </c>
       <c r="B62" t="s">
         <v>183</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="1" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>185</v>
       </c>
       <c r="B63" t="s">
         <v>186</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>188</v>
       </c>
       <c r="B64" t="s">
         <v>189</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>191</v>
       </c>
       <c r="B65" t="s">
         <v>192</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>194</v>
       </c>
       <c r="B66" t="s">
         <v>195</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>197</v>
       </c>
       <c r="B67" t="s">
         <v>198</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>200</v>
       </c>
       <c r="B68" t="s">
         <v>201</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>203</v>
       </c>
       <c r="B69" t="s">
         <v>204</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>206</v>
       </c>
       <c r="B70" t="s">
         <v>207</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>209</v>
       </c>
       <c r="B71" t="s">
         <v>210</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>212</v>
       </c>
       <c r="B72" t="s">
         <v>213</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>215</v>
       </c>
       <c r="B73" t="s">
         <v>216</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>218</v>
       </c>
       <c r="B74" t="s">
         <v>219</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>221</v>
       </c>
       <c r="B75" t="s">
         <v>222</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>224</v>
       </c>
       <c r="B76" t="s">
         <v>225</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>227</v>
       </c>
       <c r="B77" t="s">
         <v>228</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>230</v>
       </c>
       <c r="B78" t="s">
         <v>231</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>233</v>
       </c>
       <c r="B79" t="s">
         <v>234</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>236</v>
       </c>
       <c r="B80" t="s">
         <v>237</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>239</v>
       </c>
       <c r="B81" t="s">
         <v>240</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>242</v>
       </c>
       <c r="B82" t="s">
         <v>243</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>245</v>
       </c>
       <c r="B83" t="s">
         <v>246</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>247</v>
       </c>
       <c r="B84" t="s">
         <v>248</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>250</v>
       </c>
       <c r="B85" t="s">
         <v>251</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>253</v>
       </c>
       <c r="B86" t="s">
         <v>254</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>256</v>
       </c>
       <c r="B87" t="s">
         <v>257</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>258</v>
       </c>
       <c r="B88" t="s">
         <v>259</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>261</v>
       </c>
       <c r="B89" t="s">
         <v>262</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>264</v>
       </c>
       <c r="B90" t="s">
         <v>265</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>267</v>
       </c>
       <c r="B91" t="s">
         <v>268</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>270</v>
       </c>
       <c r="B92" t="s">
         <v>271</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>272</v>
       </c>
       <c r="B93" t="s">
         <v>273</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>275</v>
       </c>
       <c r="B94" t="s">
         <v>276</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>277</v>
       </c>
       <c r="B95" t="s">
         <v>278</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>280</v>
       </c>
       <c r="B96" t="s">
         <v>281</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>283</v>
       </c>
       <c r="B97" t="s">
         <v>284</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>286</v>
       </c>
       <c r="B98" t="s">
         <v>287</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>289</v>
       </c>
       <c r="B99" t="s">
         <v>290</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1">
+        <v>20419</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="12" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="B100" t="s">
         <v>292</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" s="1">
+        <v>37157</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>293</v>
       </c>
-      <c r="C100" t="s">
+      <c r="B101" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="12" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="C101" s="1">
+        <v>19178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>295</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B102" t="s">
         <v>296</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="12" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>298</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>299</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="12" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>301</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B104" t="s">
         <v>302</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" s="1" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="12" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>304</v>
-      </c>
-      <c r="B104" t="s">
-        <v>305</v>
-      </c>
-      <c r="C104" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B105" t="s">
-        <v>308</v>
-      </c>
-      <c r="C105" t="s">
-        <v>309</v>
+        <v>305</v>
+      </c>
+      <c r="C105" s="1">
+        <v>23266</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
-      </c>
-      <c r="C106" t="s">
-        <v>311</v>
+        <v>308</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
-      </c>
-      <c r="C107" t="s">
-        <v>314</v>
+        <v>311</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B108" t="s">
-        <v>318</v>
-      </c>
-      <c r="C108" t="s">
-        <v>317</v>
+        <v>314</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>315</v>
+      </c>
+      <c r="B109" t="s">
+        <v>317</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>318</v>
+      </c>
+      <c r="B110" t="s">
+        <v>321</v>
+      </c>
+      <c r="C110" s="1">
+        <v>36535</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>319</v>
       </c>
-      <c r="B109" t="s">
-        <v>321</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="B111" t="s">
+        <v>322</v>
+      </c>
+      <c r="C111" s="1">
+        <v>27976</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>320</v>
+      </c>
+      <c r="B112" t="s">
+        <v>323</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
